--- a/WorkBot/main/data/order_archive/Peters Supply/Peters Supply_Triphammer_20260515.xlsx
+++ b/WorkBot/main/data/order_archive/Peters Supply/Peters Supply_Triphammer_20260515.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,27 +605,6 @@
         <v>47.34</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PS 1077861</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Wrapping Sheets - 15x15 (poly)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>64</v>
-      </c>
-      <c r="E12" t="n">
-        <v>64</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
